--- a/output_tcc_var_selic_ativ_espec_Modelo8_subamostras/2003_2014/tabelas/johansen_Oleo_diesel_IPCA_Transporte.xlsx
+++ b/output_tcc_var_selic_ativ_espec_Modelo8_subamostras/2003_2014/tabelas/johansen_Oleo_diesel_IPCA_Transporte.xlsx
@@ -440,7 +440,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120.1303590520718</v>
+        <v>120.1303590520702</v>
       </c>
       <c r="B2" t="n">
         <v>120.3673</v>
@@ -454,7 +454,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>80.79518873601275</v>
+        <v>80.79518873601178</v>
       </c>
       <c r="B3" t="n">
         <v>91.10899999999999</v>
@@ -468,7 +468,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>51.34246943691433</v>
+        <v>51.34246943691343</v>
       </c>
       <c r="B4" t="n">
         <v>65.8202</v>
@@ -482,7 +482,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>29.49736989764859</v>
+        <v>29.49736989764832</v>
       </c>
       <c r="B5" t="n">
         <v>44.4929</v>
@@ -496,7 +496,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15.25561542085795</v>
+        <v>15.25561542085751</v>
       </c>
       <c r="B6" t="n">
         <v>27.0669</v>
@@ -510,7 +510,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>7.071777820272232</v>
+        <v>7.071777820272169</v>
       </c>
       <c r="B7" t="n">
         <v>13.4294</v>
@@ -524,7 +524,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1.53426340876177</v>
+        <v>1.534263408761707</v>
       </c>
       <c r="B8" t="n">
         <v>2.7055</v>
